--- a/backend/signal_logs/backfill_reports/complete_report_2026-08-24_to_2026-08-31.xlsx
+++ b/backend/signal_logs/backfill_reports/complete_report_2026-08-24_to_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3461,6 +3461,393 @@
         <v>-1.7</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Closed down ~19.2 (-7.0% from entry)</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Closed down ~22.0 (-16.7% from entry)</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>-16.7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Target 3 Hit</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>43.76</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Closed down ~125.0 (-3.0% from entry)</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>-24.73</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Closed flat ~1.5 (+0.0% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Closed down ~62.35 (-5.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Closed up ~5.2 (+2.0% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
